--- a/artfynd/A 38318-2026 artfynd.xlsx
+++ b/artfynd/A 38318-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137175128</v>
       </c>
       <c r="B2" t="n">
-        <v>99350</v>
+        <v>99352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137175137</v>
       </c>
       <c r="B3" t="n">
-        <v>99350</v>
+        <v>99352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137175141</v>
       </c>
       <c r="B4" t="n">
-        <v>99350</v>
+        <v>99352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137175121</v>
       </c>
       <c r="B5" t="n">
-        <v>102498</v>
+        <v>102500</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137175132</v>
       </c>
       <c r="B6" t="n">
-        <v>102498</v>
+        <v>102500</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137175136</v>
       </c>
       <c r="B7" t="n">
-        <v>102498</v>
+        <v>102500</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137175119</v>
       </c>
       <c r="B8" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137175120</v>
       </c>
       <c r="B9" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137175123</v>
       </c>
       <c r="B10" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137175124</v>
       </c>
       <c r="B11" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137175133</v>
       </c>
       <c r="B12" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137175135</v>
       </c>
       <c r="B13" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137175138</v>
       </c>
       <c r="B14" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 38318-2026 artfynd.xlsx
+++ b/artfynd/A 38318-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137175128</v>
       </c>
       <c r="B2" t="n">
-        <v>99352</v>
+        <v>99354</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137175137</v>
       </c>
       <c r="B3" t="n">
-        <v>99352</v>
+        <v>99354</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137175141</v>
       </c>
       <c r="B4" t="n">
-        <v>99352</v>
+        <v>99354</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137175121</v>
       </c>
       <c r="B5" t="n">
-        <v>102500</v>
+        <v>102502</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137175132</v>
       </c>
       <c r="B6" t="n">
-        <v>102500</v>
+        <v>102502</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137175136</v>
       </c>
       <c r="B7" t="n">
-        <v>102500</v>
+        <v>102502</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137175119</v>
       </c>
       <c r="B8" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137175120</v>
       </c>
       <c r="B9" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137175123</v>
       </c>
       <c r="B10" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137175124</v>
       </c>
       <c r="B11" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137175133</v>
       </c>
       <c r="B12" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137175135</v>
       </c>
       <c r="B13" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137175138</v>
       </c>
       <c r="B14" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 38318-2026 artfynd.xlsx
+++ b/artfynd/A 38318-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137175128</v>
       </c>
       <c r="B2" t="n">
-        <v>99354</v>
+        <v>99367</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137175137</v>
       </c>
       <c r="B3" t="n">
-        <v>99354</v>
+        <v>99367</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137175141</v>
       </c>
       <c r="B4" t="n">
-        <v>99354</v>
+        <v>99367</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137175121</v>
       </c>
       <c r="B5" t="n">
-        <v>102502</v>
+        <v>102515</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137175132</v>
       </c>
       <c r="B6" t="n">
-        <v>102502</v>
+        <v>102515</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137175136</v>
       </c>
       <c r="B7" t="n">
-        <v>102502</v>
+        <v>102515</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137175119</v>
       </c>
       <c r="B8" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137175120</v>
       </c>
       <c r="B9" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137175123</v>
       </c>
       <c r="B10" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137175124</v>
       </c>
       <c r="B11" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137175133</v>
       </c>
       <c r="B12" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137175135</v>
       </c>
       <c r="B13" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137175138</v>
       </c>
       <c r="B14" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 38318-2026 artfynd.xlsx
+++ b/artfynd/A 38318-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137175128</v>
       </c>
       <c r="B2" t="n">
-        <v>99367</v>
+        <v>99369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137175137</v>
       </c>
       <c r="B3" t="n">
-        <v>99367</v>
+        <v>99369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137175141</v>
       </c>
       <c r="B4" t="n">
-        <v>99367</v>
+        <v>99369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137175121</v>
       </c>
       <c r="B5" t="n">
-        <v>102515</v>
+        <v>102517</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137175132</v>
       </c>
       <c r="B6" t="n">
-        <v>102515</v>
+        <v>102517</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137175136</v>
       </c>
       <c r="B7" t="n">
-        <v>102515</v>
+        <v>102517</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137175119</v>
       </c>
       <c r="B8" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137175120</v>
       </c>
       <c r="B9" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137175123</v>
       </c>
       <c r="B10" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137175124</v>
       </c>
       <c r="B11" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137175133</v>
       </c>
       <c r="B12" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137175135</v>
       </c>
       <c r="B13" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137175138</v>
       </c>
       <c r="B14" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 38318-2026 artfynd.xlsx
+++ b/artfynd/A 38318-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137175128</v>
       </c>
       <c r="B2" t="n">
-        <v>99369</v>
+        <v>99372</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137175137</v>
       </c>
       <c r="B3" t="n">
-        <v>99369</v>
+        <v>99372</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137175141</v>
       </c>
       <c r="B4" t="n">
-        <v>99369</v>
+        <v>99372</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137175121</v>
       </c>
       <c r="B5" t="n">
-        <v>102517</v>
+        <v>102520</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137175132</v>
       </c>
       <c r="B6" t="n">
-        <v>102517</v>
+        <v>102520</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137175136</v>
       </c>
       <c r="B7" t="n">
-        <v>102517</v>
+        <v>102520</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137175119</v>
       </c>
       <c r="B8" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137175120</v>
       </c>
       <c r="B9" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137175123</v>
       </c>
       <c r="B10" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137175124</v>
       </c>
       <c r="B11" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137175133</v>
       </c>
       <c r="B12" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137175135</v>
       </c>
       <c r="B13" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137175138</v>
       </c>
       <c r="B14" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 38318-2026 artfynd.xlsx
+++ b/artfynd/A 38318-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137175128</v>
       </c>
       <c r="B2" t="n">
-        <v>99372</v>
+        <v>99382</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137175137</v>
       </c>
       <c r="B3" t="n">
-        <v>99372</v>
+        <v>99382</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137175141</v>
       </c>
       <c r="B4" t="n">
-        <v>99372</v>
+        <v>99382</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137175121</v>
       </c>
       <c r="B5" t="n">
-        <v>102520</v>
+        <v>102535</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137175132</v>
       </c>
       <c r="B6" t="n">
-        <v>102520</v>
+        <v>102535</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137175136</v>
       </c>
       <c r="B7" t="n">
-        <v>102520</v>
+        <v>102535</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137175119</v>
       </c>
       <c r="B8" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137175120</v>
       </c>
       <c r="B9" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137175123</v>
       </c>
       <c r="B10" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137175124</v>
       </c>
       <c r="B11" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137175133</v>
       </c>
       <c r="B12" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137175135</v>
       </c>
       <c r="B13" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137175138</v>
       </c>
       <c r="B14" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 38318-2026 artfynd.xlsx
+++ b/artfynd/A 38318-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137175128</v>
       </c>
       <c r="B2" t="n">
-        <v>99382</v>
+        <v>99383</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137175137</v>
       </c>
       <c r="B3" t="n">
-        <v>99382</v>
+        <v>99383</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137175141</v>
       </c>
       <c r="B4" t="n">
-        <v>99382</v>
+        <v>99383</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137175121</v>
       </c>
       <c r="B5" t="n">
-        <v>102535</v>
+        <v>102536</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137175132</v>
       </c>
       <c r="B6" t="n">
-        <v>102535</v>
+        <v>102536</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137175136</v>
       </c>
       <c r="B7" t="n">
-        <v>102535</v>
+        <v>102536</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137175119</v>
       </c>
       <c r="B8" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137175120</v>
       </c>
       <c r="B9" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137175123</v>
       </c>
       <c r="B10" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137175124</v>
       </c>
       <c r="B11" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137175133</v>
       </c>
       <c r="B12" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137175135</v>
       </c>
       <c r="B13" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137175138</v>
       </c>
       <c r="B14" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 38318-2026 artfynd.xlsx
+++ b/artfynd/A 38318-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137175128</v>
       </c>
       <c r="B2" t="n">
-        <v>99383</v>
+        <v>99388</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137175137</v>
       </c>
       <c r="B3" t="n">
-        <v>99383</v>
+        <v>99388</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137175141</v>
       </c>
       <c r="B4" t="n">
-        <v>99383</v>
+        <v>99388</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137175121</v>
       </c>
       <c r="B5" t="n">
-        <v>102536</v>
+        <v>102541</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137175132</v>
       </c>
       <c r="B6" t="n">
-        <v>102536</v>
+        <v>102541</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137175136</v>
       </c>
       <c r="B7" t="n">
-        <v>102536</v>
+        <v>102541</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137175119</v>
       </c>
       <c r="B8" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137175120</v>
       </c>
       <c r="B9" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137175123</v>
       </c>
       <c r="B10" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137175124</v>
       </c>
       <c r="B11" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137175133</v>
       </c>
       <c r="B12" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137175135</v>
       </c>
       <c r="B13" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137175138</v>
       </c>
       <c r="B14" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 38318-2026 artfynd.xlsx
+++ b/artfynd/A 38318-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137175128</v>
       </c>
       <c r="B2" t="n">
-        <v>99388</v>
+        <v>99390</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137175137</v>
       </c>
       <c r="B3" t="n">
-        <v>99388</v>
+        <v>99390</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137175141</v>
       </c>
       <c r="B4" t="n">
-        <v>99388</v>
+        <v>99390</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137175121</v>
       </c>
       <c r="B5" t="n">
-        <v>102541</v>
+        <v>102544</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137175132</v>
       </c>
       <c r="B6" t="n">
-        <v>102541</v>
+        <v>102544</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137175136</v>
       </c>
       <c r="B7" t="n">
-        <v>102541</v>
+        <v>102544</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137175119</v>
       </c>
       <c r="B8" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137175120</v>
       </c>
       <c r="B9" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137175123</v>
       </c>
       <c r="B10" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137175124</v>
       </c>
       <c r="B11" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137175133</v>
       </c>
       <c r="B12" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137175135</v>
       </c>
       <c r="B13" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137175138</v>
       </c>
       <c r="B14" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 38318-2026 artfynd.xlsx
+++ b/artfynd/A 38318-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137175128</v>
       </c>
       <c r="B2" t="n">
-        <v>99390</v>
+        <v>99396</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137175137</v>
       </c>
       <c r="B3" t="n">
-        <v>99390</v>
+        <v>99396</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137175141</v>
       </c>
       <c r="B4" t="n">
-        <v>99390</v>
+        <v>99396</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137175121</v>
       </c>
       <c r="B5" t="n">
-        <v>102544</v>
+        <v>102550</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137175132</v>
       </c>
       <c r="B6" t="n">
-        <v>102544</v>
+        <v>102550</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137175136</v>
       </c>
       <c r="B7" t="n">
-        <v>102544</v>
+        <v>102550</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137175119</v>
       </c>
       <c r="B8" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137175120</v>
       </c>
       <c r="B9" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137175123</v>
       </c>
       <c r="B10" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137175124</v>
       </c>
       <c r="B11" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137175133</v>
       </c>
       <c r="B12" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137175135</v>
       </c>
       <c r="B13" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137175138</v>
       </c>
       <c r="B14" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 38318-2026 artfynd.xlsx
+++ b/artfynd/A 38318-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137175128</v>
       </c>
       <c r="B2" t="n">
-        <v>99396</v>
+        <v>99408</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137175137</v>
       </c>
       <c r="B3" t="n">
-        <v>99396</v>
+        <v>99408</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137175141</v>
       </c>
       <c r="B4" t="n">
-        <v>99396</v>
+        <v>99408</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137175121</v>
       </c>
       <c r="B5" t="n">
-        <v>102550</v>
+        <v>102562</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137175132</v>
       </c>
       <c r="B6" t="n">
-        <v>102550</v>
+        <v>102562</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137175136</v>
       </c>
       <c r="B7" t="n">
-        <v>102550</v>
+        <v>102562</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137175119</v>
       </c>
       <c r="B8" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137175120</v>
       </c>
       <c r="B9" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137175123</v>
       </c>
       <c r="B10" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137175124</v>
       </c>
       <c r="B11" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137175133</v>
       </c>
       <c r="B12" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137175135</v>
       </c>
       <c r="B13" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137175138</v>
       </c>
       <c r="B14" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 38318-2026 artfynd.xlsx
+++ b/artfynd/A 38318-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137175128</v>
       </c>
       <c r="B2" t="n">
-        <v>99408</v>
+        <v>99409</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137175137</v>
       </c>
       <c r="B3" t="n">
-        <v>99408</v>
+        <v>99409</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137175141</v>
       </c>
       <c r="B4" t="n">
-        <v>99408</v>
+        <v>99409</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137175121</v>
       </c>
       <c r="B5" t="n">
-        <v>102562</v>
+        <v>102563</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137175132</v>
       </c>
       <c r="B6" t="n">
-        <v>102562</v>
+        <v>102563</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137175136</v>
       </c>
       <c r="B7" t="n">
-        <v>102562</v>
+        <v>102563</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137175119</v>
       </c>
       <c r="B8" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137175120</v>
       </c>
       <c r="B9" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137175123</v>
       </c>
       <c r="B10" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137175124</v>
       </c>
       <c r="B11" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137175133</v>
       </c>
       <c r="B12" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137175135</v>
       </c>
       <c r="B13" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137175138</v>
       </c>
       <c r="B14" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 38318-2026 artfynd.xlsx
+++ b/artfynd/A 38318-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137175128</v>
       </c>
       <c r="B2" t="n">
-        <v>99409</v>
+        <v>99412</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137175137</v>
       </c>
       <c r="B3" t="n">
-        <v>99409</v>
+        <v>99412</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137175141</v>
       </c>
       <c r="B4" t="n">
-        <v>99409</v>
+        <v>99412</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137175121</v>
       </c>
       <c r="B5" t="n">
-        <v>102563</v>
+        <v>102566</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137175132</v>
       </c>
       <c r="B6" t="n">
-        <v>102563</v>
+        <v>102566</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137175136</v>
       </c>
       <c r="B7" t="n">
-        <v>102563</v>
+        <v>102566</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137175119</v>
       </c>
       <c r="B8" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137175120</v>
       </c>
       <c r="B9" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137175123</v>
       </c>
       <c r="B10" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137175124</v>
       </c>
       <c r="B11" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137175133</v>
       </c>
       <c r="B12" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137175135</v>
       </c>
       <c r="B13" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137175138</v>
       </c>
       <c r="B14" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 38318-2026 artfynd.xlsx
+++ b/artfynd/A 38318-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137175128</v>
       </c>
       <c r="B2" t="n">
-        <v>99412</v>
+        <v>99416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137175137</v>
       </c>
       <c r="B3" t="n">
-        <v>99412</v>
+        <v>99416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137175141</v>
       </c>
       <c r="B4" t="n">
-        <v>99412</v>
+        <v>99416</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137175121</v>
       </c>
       <c r="B5" t="n">
-        <v>102566</v>
+        <v>102570</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137175132</v>
       </c>
       <c r="B6" t="n">
-        <v>102566</v>
+        <v>102570</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137175136</v>
       </c>
       <c r="B7" t="n">
-        <v>102566</v>
+        <v>102570</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137175119</v>
       </c>
       <c r="B8" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137175120</v>
       </c>
       <c r="B9" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137175123</v>
       </c>
       <c r="B10" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137175124</v>
       </c>
       <c r="B11" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137175133</v>
       </c>
       <c r="B12" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137175135</v>
       </c>
       <c r="B13" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137175138</v>
       </c>
       <c r="B14" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
